--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="B2:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1492,7 +1492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1643,6 +1643,28 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>#seed口径</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>统计口径定版:粗筛 1-2 seed;确认轮全 3 seed;5 seed 仅对最终旗舰配置后补。全主线纯计算 ~81h</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>3→5 seed 每配置 +70% 成本仅换 CI 窄 1.3×;中间态 Δ 5 seed 也救不活,功效花在刀刃上</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -1492,7 +1492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1665,6 +1665,28 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>#N1判定</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N1 多库语料轨判死:LP AUPRC 0.6870 vs B0 0.7177(Δ−3.07pt),不满足'PTB-XL≥B0'主判据;主线维持 PTB-XL 单库语料</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>异质语料稀释 PTB-XL 特异形态;混合比例/两阶段课程为附录级改道,不占主线;省 GPU(粗筛 1.4h/次)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1137,12 +1137,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22.4" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1">
+    <row r="12" ht="118" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>E008</t>
@@ -1422,57 +1422,89 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>待启动</t>
+          <t>2026-09-15 启动</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>主线 S1: D9 VICReg 化粗筛(1-2 seed,LP,Δ≥1.0pt 过线)+batch 曲线 128/512,N4 附带</t>
+          <t>主线 S1: D9 VICReg 化粗筛(vicreg/bn/ln 三变体, seed 0/2)+batch 曲线 128/512,N4 附带</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>S-M,改损失不动数据管线</t>
+          <t>PTB-XL 单库语料,B0 同配置</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>官方系数 25/25/1: vicreg s0 0.6981(−1.96pt) / s2 0.6830(−3.47pt);+BN 0.6534(−6.43pt);+LN 0.6798(−3.79pt)——均 vs B0 0.7177;vicreg seed 方差 1.5pt &gt;&gt; B0 ±0.4pt</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>排队中</t>
+          <t>粗筛全负;仅存下一步=系数重标定(D9-R1)+最小防塌补丁(D9-lite)+batch 曲线;B0 s2 配对基准 13:15</t>
         </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:37 判定</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>多库混合预训练(38,682条)生死判定</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>seed 0, 200ep, batch 128, B0 原版目标</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LP AUPRC 0.6870 vs B0 0.7177 (Δ−3.07pt), AUROC −0.76pt</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>❌ 不过线:不切换语料,G2 取消;混合比例/两阶段课程留作附录级改道</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="54" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>W0-4</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>服务器 LP 复现校验(本机 RTX4090, DL env torch2.5.1+cu121)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>checkpoint ptxl_gamma08, data/ptbxl 体系A, seed 0</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>AUROC 0.9126 / AUPRC 0.7173 vs E001 锚点 0.7177,Δ=0.04pt</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>✅ 通过(±0.5pt 内),管线与 E001 行为一致</t>
         </is>
@@ -1492,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1643,50 +1675,6 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>#seed口径</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>统计口径定版:粗筛 1-2 seed;确认轮全 3 seed;5 seed 仅对最终旗舰配置后补。全主线纯计算 ~81h</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>3→5 seed 每配置 +70% 成本仅换 CI 窄 1.3×;中间态 Δ 5 seed 也救不活,功效花在刀刃上</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>#N1判定</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>N1 多库语料轨判死:LP AUPRC 0.6870 vs B0 0.7177(Δ−3.07pt),不满足'PTB-XL≥B0'主判据;主线维持 PTB-XL 单库语料</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>异质语料稀释 PTB-XL 特异形态;混合比例/两阶段课程为附录级改道,不占主线;省 GPU(粗筛 1.4h/次)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="B2:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="B2:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1675,6 +1675,28 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="134" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>#策略转向</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>成稿策略定版:放弃单点冲顶刊,改'全量微筛选→正收益拼接→以量取胜'工程报告路线。筛选保留标准从'Δ≥1pt'改为'3 seed 符号一致(如 E006 3/3)',微正收益全部入库不丢弃;正收益模块逐一拼接+交互核验,产 SD-LFBT 组合模型与逐模块归因报告</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>约束:防噪声堆叠——E003 自动复合失败教训,拼接前必须过符号一致门+2x2 交互核验;投稿档位 JBHI/BSPC/CBM 等应用刊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1697,6 +1697,28 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="102" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>#方向终版</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>主线定版为 M 筛选矩阵(工程旋钮:损失/增强/采样/训练级);D4 换主干、D3 解耦、D7 加支路等结构创新全部撤出主线;成稿=SD-LFBT 组合模型+逐模块归因+鲁棒画像,JBHI/BSPC/CBM 档</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>微弱贡献也是贡献,堆量取胜;拼接纪律:3seed 符号一致门+交互核验防噪声堆叠(E003 教训)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1719,6 +1719,28 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="102" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>#边界修正</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>结构创新边界澄清:仅'换主干'类大结构创新出局(D4);D3(projector 分头+约束路由)、D7(并联重建支路)属模块级小创新,重回主线 M 矩阵。判据:主干不动+开关关闭逐位回 B0+架构非论文主张</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>M 矩阵候选 12 个:D1L/D3/D7/D9-lite/D9-R1/P1/S1/N3/N4/N6/N8/GRN重核</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12.7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>🟢 S2 主创新</t>
+          <t>🟢 M 矩阵候选(模块级,2026-09-16 回归)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>01 §4.2</t>
+          <t>01 §五 v3.0</t>
         </is>
       </c>
     </row>
@@ -661,17 +661,17 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>🟡 S3,带硬前提 G-D4 参数对齐对照</t>
+          <t>❌ 出局(换主干=大结构创新,2026-09-16)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>E004 轻量适配器已终止,须换真主干</t>
+          <t>工程报告路线不做结构创新;除非顺带出正号按普通模块入 M 库</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>01 §4.4</t>
+          <t>01 §五 v3.0</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>🟢 S4 冲点</t>
+          <t>🟢 M 矩阵候选(模块级并联支路,期望最高)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>01 §4.5</t>
+          <t>01 §五 v3.0</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1675,72 +1675,6 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="134" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>#策略转向</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>成稿策略定版:放弃单点冲顶刊,改'全量微筛选→正收益拼接→以量取胜'工程报告路线。筛选保留标准从'Δ≥1pt'改为'3 seed 符号一致(如 E006 3/3)',微正收益全部入库不丢弃;正收益模块逐一拼接+交互核验,产 SD-LFBT 组合模型与逐模块归因报告</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>约束:防噪声堆叠——E003 自动复合失败教训,拼接前必须过符号一致门+2x2 交互核验;投稿档位 JBHI/BSPC/CBM 等应用刊</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="102" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>#方向终版</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>主线定版为 M 筛选矩阵(工程旋钮:损失/增强/采样/训练级);D4 换主干、D3 解耦、D7 加支路等结构创新全部撤出主线;成稿=SD-LFBT 组合模型+逐模块归因+鲁棒画像,JBHI/BSPC/CBM 档</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>微弱贡献也是贡献,堆量取胜;拼接纪律:3seed 符号一致门+交互核验防噪声堆叠(E003 教训)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="102" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>#边界修正</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>结构创新边界澄清:仅'换主干'类大结构创新出局(D4);D3(projector 分头+约束路由)、D7(并联重建支路)属模块级小创新,重回主线 M 矩阵。判据:主干不动+开关关闭逐位回 B0+架构非论文主张</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>M 矩阵候选 12 个:D1L/D3/D7/D9-lite/D9-R1/P1/S1/N3/N4/N6/N8/GRN重核</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="B2:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="B2:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1675,6 +1675,28 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="86" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>#一篇收敛</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>发表目标收敛为一篇小论文(SD-LFBT 工程报告):鲁棒评估=结果章一节,负结果链=motivation 一张表,不做独立成篇;实验量相应缩减</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>01 §五 v3.1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>

--- a/LFBT实验方向清单.xlsx
+++ b/LFBT实验方向清单.xlsx
@@ -1524,7 +1524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1697,6 +1697,28 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="102" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>#D9结案</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>D9 全族 6/6 归档:官方系数 s0 −1.96/s2 −4.28(配对)、+BN −6.43、+LN −3.79、重标定R1 −10.7、lite −1.30。三项化任何形态与 γ 双层聚合不兼容;六点系数曲线进 motivation</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>M 第一批(D1L/NEG/N4)已自动开跑,明早出入库判定</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
